--- a/docentes/Ramírez Vargas Miranda Alejandra - Estadisticos 20241.xlsx
+++ b/docentes/Ramírez Vargas Miranda Alejandra - Estadisticos 20241.xlsx
@@ -85,22 +85,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>DAFNE</t>
-  </si>
-  <si>
-    <t>ALIN MARIEL</t>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>DANIELA LILI</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
   </si>
 </sst>
 </file>
@@ -504,16 +504,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>69.7</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -696,16 +696,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>78.79000000000001</v>
+      </c>
+      <c r="H2">
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -719,16 +722,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>97.56</v>
+      </c>
+      <c r="H3">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -742,16 +748,19 @@
         <v>40</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>40</v>
       </c>
-      <c r="E4">
-        <v>40</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -765,16 +774,19 @@
         <v>36</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>36</v>
       </c>
-      <c r="E5">
-        <v>36</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>9.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -788,16 +800,19 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="H6">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -811,16 +826,19 @@
         <v>25</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>25</v>
       </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -876,16 +894,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -911,7 +929,7 @@
         <v>97.56</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -963,7 +981,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1015,7 +1033,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1057,7 +1075,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920357</v>
+        <v>24330051920330</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1075,12 +1093,12 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920246</v>
+        <v>22330051920116</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1092,13 +1110,13 @@
         <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ramírez Vargas Miranda Alejandra - Estadisticos 20241.xlsx
+++ b/docentes/Ramírez Vargas Miranda Alejandra - Estadisticos 20241.xlsx
@@ -85,7 +85,7 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>TORRES</t>
   </si>
   <si>
     <t>ROJAS</t>
@@ -97,7 +97,7 @@
     <t>SOTO</t>
   </si>
   <si>
-    <t>DANIELA LILI</t>
+    <t>ERIKA VALERIA</t>
   </si>
   <si>
     <t>ANDRES</t>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920330</v>
+        <v>24330051920238</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>

--- a/docentes/Ramírez Vargas Miranda Alejandra - Estadisticos 20241.xlsx
+++ b/docentes/Ramírez Vargas Miranda Alejandra - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -85,16 +85,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>SOTO</t>
+  </si>
+  <si>
+    <t>ANGEL ISMAEL</t>
+  </si>
+  <si>
+    <t>DANIELA LILI</t>
   </si>
   <si>
     <t>ERIKA VALERIA</t>
@@ -1043,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1075,16 +1090,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920238</v>
+        <v>24330051920239</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1093,29 +1108,75 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920116</v>
+        <v>24330051920330</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>24330051920238</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920116</v>
+      </c>
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
         <v>11</v>
       </c>
-      <c r="G3">
+      <c r="G5">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Ramírez Vargas Miranda Alejandra - Estadisticos 20241.xlsx
+++ b/docentes/Ramírez Vargas Miranda Alejandra - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -85,34 +85,43 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>SOTO</t>
   </si>
   <si>
+    <t>DANIELA LILI</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>ERIKA VALERIA</t>
+  </si>
+  <si>
     <t>ANGEL ISMAEL</t>
-  </si>
-  <si>
-    <t>DANIELA LILI</t>
-  </si>
-  <si>
-    <t>ERIKA VALERIA</t>
   </si>
   <si>
     <t>ANDRES</t>
@@ -565,7 +574,7 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -574,13 +583,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -617,7 +626,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -626,13 +635,13 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -643,7 +652,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -652,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -760,7 +769,7 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -769,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -812,7 +821,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -821,13 +830,13 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -838,7 +847,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -847,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -955,7 +964,7 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -964,13 +973,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -996,7 +1005,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1007,7 +1016,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1016,10 +1025,10 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H6">
         <v>8.300000000000001</v>
@@ -1033,7 +1042,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1042,13 +1051,13 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G7">
         <v>100</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -1058,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1090,16 +1099,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920239</v>
+        <v>24330051920330</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1108,27 +1117,27 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920330</v>
+        <v>22330051920356</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1145,7 +1154,7 @@
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1159,24 +1168,47 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920116</v>
+        <v>24330051920239</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Ramírez Vargas Miranda Alejandra - Estadisticos 20241.xlsx
+++ b/docentes/Ramírez Vargas Miranda Alejandra - Estadisticos 20241.xlsx
@@ -88,43 +88,43 @@
     <t>VASQUEZ</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>ALFONSO</t>
   </si>
   <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
     <t>SOTO</t>
   </si>
   <si>
     <t>DANIELA LILI</t>
   </si>
   <si>
+    <t>ANGEL ISMAEL</t>
+  </si>
+  <si>
     <t>JOSUE GUSTAVO</t>
   </si>
   <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
     <t>ERIKA VALERIA</t>
-  </si>
-  <si>
-    <t>ANGEL ISMAEL</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
   </si>
 </sst>
 </file>
@@ -1117,12 +1117,12 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920356</v>
+        <v>24330051920239</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1134,10 +1134,10 @@
         <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920238</v>
+        <v>22330051920356</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1168,22 +1168,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920239</v>
+        <v>22330051920116</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1191,25 +1191,25 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920116</v>
+        <v>24330051920238</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
         <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ramírez Vargas Miranda Alejandra - Estadisticos 20241.xlsx
+++ b/docentes/Ramírez Vargas Miranda Alejandra - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -91,13 +91,10 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TORRES</t>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>ZUNO</t>
   </si>
   <si>
     <t>PEREZ</t>
@@ -106,10 +103,10 @@
     <t>BONILLA</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>SOTO</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>DANIELA LILI</t>
@@ -118,13 +115,10 @@
     <t>ANGEL ISMAEL</t>
   </si>
   <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ERIKA VALERIA</t>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ALIN MARIEL</t>
   </si>
 </sst>
 </file>
@@ -927,7 +921,7 @@
         <v>78.79000000000001</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -944,16 +938,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>97.56</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -970,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>97.73</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1022,16 +1016,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>95.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1057,7 +1051,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1105,10 +1099,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1128,10 +1122,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1145,70 +1139,47 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920356</v>
+        <v>21330051920053</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920116</v>
+        <v>24330051920246</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920238</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
     </row>
